--- a/Data/Cleaned/Aster Retail Holdings (Excel).xlsx
+++ b/Data/Cleaned/Aster Retail Holdings (Excel).xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M501"/>
+  <dimension ref="A1:L501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,11 +490,6 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>correct_category</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
           <t>sales</t>
         </is>
       </c>
@@ -541,12 +536,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
+      <c r="L2" t="n">
         <v>611</v>
       </c>
     </row>
@@ -592,12 +582,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
+      <c r="L3" t="n">
         <v>3004</v>
       </c>
     </row>
@@ -618,7 +603,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -643,12 +628,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
+      <c r="L4" t="n">
         <v>3284</v>
       </c>
     </row>
@@ -669,7 +649,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -694,12 +674,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
+      <c r="L5" t="n">
         <v>1580</v>
       </c>
     </row>
@@ -720,7 +695,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -745,12 +720,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
+      <c r="L6" t="n">
         <v>301</v>
       </c>
     </row>
@@ -771,7 +741,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -796,12 +766,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
+      <c r="L7" t="n">
         <v>130</v>
       </c>
     </row>
@@ -822,7 +787,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -847,12 +812,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
+      <c r="L8" t="n">
         <v>251</v>
       </c>
     </row>
@@ -898,12 +858,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
+      <c r="L9" t="n">
         <v>2328</v>
       </c>
     </row>
@@ -924,7 +879,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -949,12 +904,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
+      <c r="L10" t="n">
         <v>141</v>
       </c>
     </row>
@@ -975,7 +925,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1000,12 +950,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
+      <c r="L11" t="n">
         <v>826</v>
       </c>
     </row>
@@ -1051,12 +996,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
+      <c r="L12" t="n">
         <v>928</v>
       </c>
     </row>
@@ -1077,7 +1017,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1102,12 +1042,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
+      <c r="L13" t="n">
         <v>465</v>
       </c>
     </row>
@@ -1128,7 +1063,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1153,12 +1088,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
+      <c r="L14" t="n">
         <v>776</v>
       </c>
     </row>
@@ -1204,12 +1134,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M15" t="n">
+      <c r="L15" t="n">
         <v>2444</v>
       </c>
     </row>
@@ -1255,12 +1180,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M16" t="n">
+      <c r="L16" t="n">
         <v>912</v>
       </c>
     </row>
@@ -1281,7 +1201,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1306,12 +1226,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M17" t="n">
+      <c r="L17" t="n">
         <v>3004</v>
       </c>
     </row>
@@ -1332,7 +1247,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1357,12 +1272,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M18" t="n">
+      <c r="L18" t="n">
         <v>3116</v>
       </c>
     </row>
@@ -1383,7 +1293,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1408,12 +1318,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
+      <c r="L19" t="n">
         <v>1908</v>
       </c>
     </row>
@@ -1459,12 +1364,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M20" t="n">
+      <c r="L20" t="n">
         <v>252</v>
       </c>
     </row>
@@ -1485,7 +1385,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1510,12 +1410,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M21" t="n">
+      <c r="L21" t="n">
         <v>423</v>
       </c>
     </row>
@@ -1561,12 +1456,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M22" t="n">
+      <c r="L22" t="n">
         <v>423</v>
       </c>
     </row>
@@ -1587,7 +1477,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1612,12 +1502,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M23" t="n">
+      <c r="L23" t="n">
         <v>51</v>
       </c>
     </row>
@@ -1638,7 +1523,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1663,12 +1548,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M24" t="n">
+      <c r="L24" t="n">
         <v>2456</v>
       </c>
     </row>
@@ -1689,7 +1569,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1714,12 +1594,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M25" t="n">
+      <c r="L25" t="n">
         <v>1833</v>
       </c>
     </row>
@@ -1765,12 +1640,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M26" t="n">
+      <c r="L26" t="n">
         <v>2523</v>
       </c>
     </row>
@@ -1816,12 +1686,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M27" t="n">
+      <c r="L27" t="n">
         <v>992</v>
       </c>
     </row>
@@ -1842,7 +1707,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1867,12 +1732,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M28" t="n">
+      <c r="L28" t="n">
         <v>306</v>
       </c>
     </row>
@@ -1918,12 +1778,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M29" t="n">
+      <c r="L29" t="n">
         <v>928</v>
       </c>
     </row>
@@ -1944,7 +1799,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1969,12 +1824,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M30" t="n">
+      <c r="L30" t="n">
         <v>1596</v>
       </c>
     </row>
@@ -2020,12 +1870,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M31" t="n">
+      <c r="L31" t="n">
         <v>2478</v>
       </c>
     </row>
@@ -2046,7 +1891,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -2071,12 +1916,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M32" t="n">
+      <c r="L32" t="n">
         <v>1222</v>
       </c>
     </row>
@@ -2122,12 +1962,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M33" t="n">
+      <c r="L33" t="n">
         <v>614</v>
       </c>
     </row>
@@ -2173,12 +2008,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M34" t="n">
+      <c r="L34" t="n">
         <v>2104</v>
       </c>
     </row>
@@ -2224,12 +2054,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M35" t="n">
+      <c r="L35" t="n">
         <v>390</v>
       </c>
     </row>
@@ -2250,7 +2075,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2275,12 +2100,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M36" t="n">
+      <c r="L36" t="n">
         <v>320</v>
       </c>
     </row>
@@ -2326,12 +2146,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M37" t="n">
+      <c r="L37" t="n">
         <v>1004</v>
       </c>
     </row>
@@ -2377,12 +2192,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M38" t="n">
+      <c r="L38" t="n">
         <v>1004</v>
       </c>
     </row>
@@ -2403,7 +2213,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -2428,12 +2238,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M39" t="n">
+      <c r="L39" t="n">
         <v>1894</v>
       </c>
     </row>
@@ -2454,7 +2259,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -2479,12 +2284,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M40" t="n">
+      <c r="L40" t="n">
         <v>921</v>
       </c>
     </row>
@@ -2505,7 +2305,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -2530,12 +2330,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M41" t="n">
+      <c r="L41" t="n">
         <v>3364</v>
       </c>
     </row>
@@ -2556,7 +2351,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -2581,12 +2376,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M42" t="n">
+      <c r="L42" t="n">
         <v>1311</v>
       </c>
     </row>
@@ -2607,7 +2397,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -2632,12 +2422,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M43" t="n">
+      <c r="L43" t="n">
         <v>2322</v>
       </c>
     </row>
@@ -2658,7 +2443,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -2683,12 +2468,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M44" t="n">
+      <c r="L44" t="n">
         <v>1730</v>
       </c>
     </row>
@@ -2709,7 +2489,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -2734,12 +2514,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M45" t="n">
+      <c r="L45" t="n">
         <v>1204</v>
       </c>
     </row>
@@ -2785,12 +2560,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M46" t="n">
+      <c r="L46" t="n">
         <v>255</v>
       </c>
     </row>
@@ -2811,7 +2581,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2836,12 +2606,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M47" t="n">
+      <c r="L47" t="n">
         <v>957</v>
       </c>
     </row>
@@ -2862,7 +2627,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2887,12 +2652,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M48" t="n">
+      <c r="L48" t="n">
         <v>1020</v>
       </c>
     </row>
@@ -2913,7 +2673,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2938,12 +2698,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M49" t="n">
+      <c r="L49" t="n">
         <v>3648</v>
       </c>
     </row>
@@ -2964,7 +2719,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2989,12 +2744,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M50" t="n">
+      <c r="L50" t="n">
         <v>1894</v>
       </c>
     </row>
@@ -3015,7 +2765,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -3040,12 +2790,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M51" t="n">
+      <c r="L51" t="n">
         <v>2463</v>
       </c>
     </row>
@@ -3091,12 +2836,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M52" t="n">
+      <c r="L52" t="n">
         <v>2337</v>
       </c>
     </row>
@@ -3117,7 +2857,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -3142,12 +2882,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M53" t="n">
+      <c r="L53" t="n">
         <v>437</v>
       </c>
     </row>
@@ -3168,7 +2903,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -3193,12 +2928,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M54" t="n">
+      <c r="L54" t="n">
         <v>423</v>
       </c>
     </row>
@@ -3219,7 +2949,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -3244,12 +2974,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M55" t="n">
+      <c r="L55" t="n">
         <v>319</v>
       </c>
     </row>
@@ -3270,7 +2995,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -3295,12 +3020,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M56" t="n">
+      <c r="L56" t="n">
         <v>2523</v>
       </c>
     </row>
@@ -3346,12 +3066,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M57" t="n">
+      <c r="L57" t="n">
         <v>602</v>
       </c>
     </row>
@@ -3397,12 +3112,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M58" t="n">
+      <c r="L58" t="n">
         <v>1311</v>
       </c>
     </row>
@@ -3448,12 +3158,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M59" t="n">
+      <c r="L59" t="n">
         <v>826</v>
       </c>
     </row>
@@ -3474,7 +3179,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -3499,12 +3204,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M60" t="n">
+      <c r="L60" t="n">
         <v>389</v>
       </c>
     </row>
@@ -3550,12 +3250,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M61" t="n">
+      <c r="L61" t="n">
         <v>1504</v>
       </c>
     </row>
@@ -3601,12 +3296,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M62" t="n">
+      <c r="L62" t="n">
         <v>2943</v>
       </c>
     </row>
@@ -3627,7 +3317,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -3652,12 +3342,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M63" t="n">
+      <c r="L63" t="n">
         <v>423</v>
       </c>
     </row>
@@ -3678,7 +3363,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -3703,12 +3388,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M64" t="n">
+      <c r="L64" t="n">
         <v>602</v>
       </c>
     </row>
@@ -3754,12 +3434,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M65" t="n">
+      <c r="L65" t="n">
         <v>252</v>
       </c>
     </row>
@@ -3805,12 +3480,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M66" t="n">
+      <c r="L66" t="n">
         <v>306</v>
       </c>
     </row>
@@ -3831,7 +3501,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -3856,12 +3526,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M67" t="n">
+      <c r="L67" t="n">
         <v>865</v>
       </c>
     </row>
@@ -3882,7 +3547,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -3907,12 +3572,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M68" t="n">
+      <c r="L68" t="n">
         <v>1311</v>
       </c>
     </row>
@@ -3933,7 +3593,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -3958,12 +3618,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M69" t="n">
+      <c r="L69" t="n">
         <v>2976</v>
       </c>
     </row>
@@ -4009,12 +3664,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M70" t="n">
+      <c r="L70" t="n">
         <v>1962</v>
       </c>
     </row>
@@ -4035,7 +3685,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -4060,12 +3710,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M71" t="n">
+      <c r="L71" t="n">
         <v>1548</v>
       </c>
     </row>
@@ -4086,7 +3731,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -4111,12 +3756,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M72" t="n">
+      <c r="L72" t="n">
         <v>2232</v>
       </c>
     </row>
@@ -4137,7 +3777,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -4162,12 +3802,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M73" t="n">
+      <c r="L73" t="n">
         <v>871</v>
       </c>
     </row>
@@ -4188,7 +3823,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -4213,12 +3848,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M74" t="n">
+      <c r="L74" t="n">
         <v>153</v>
       </c>
     </row>
@@ -4264,12 +3894,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M75" t="n">
+      <c r="L75" t="n">
         <v>633</v>
       </c>
     </row>
@@ -4290,7 +3915,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -4315,12 +3940,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M76" t="n">
+      <c r="L76" t="n">
         <v>3788</v>
       </c>
     </row>
@@ -4341,7 +3961,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -4366,12 +3986,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M77" t="n">
+      <c r="L77" t="n">
         <v>2307</v>
       </c>
     </row>
@@ -4392,7 +4007,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -4417,12 +4032,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M78" t="n">
+      <c r="L78" t="n">
         <v>155</v>
       </c>
     </row>
@@ -4443,7 +4053,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -4468,12 +4078,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M79" t="n">
+      <c r="L79" t="n">
         <v>1580</v>
       </c>
     </row>
@@ -4494,7 +4099,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -4519,12 +4124,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M80" t="n">
+      <c r="L80" t="n">
         <v>615</v>
       </c>
     </row>
@@ -4545,7 +4145,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -4570,12 +4170,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M81" t="n">
+      <c r="L81" t="n">
         <v>2020</v>
       </c>
     </row>
@@ -4621,12 +4216,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M82" t="n">
+      <c r="L82" t="n">
         <v>2016</v>
       </c>
     </row>
@@ -4647,7 +4237,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -4672,12 +4262,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M83" t="n">
+      <c r="L83" t="n">
         <v>832</v>
       </c>
     </row>
@@ -4698,7 +4283,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -4723,12 +4308,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M84" t="n">
+      <c r="L84" t="n">
         <v>255</v>
       </c>
     </row>
@@ -4774,12 +4354,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M85" t="n">
+      <c r="L85" t="n">
         <v>1842</v>
       </c>
     </row>
@@ -4825,12 +4400,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M86" t="n">
+      <c r="L86" t="n">
         <v>2913</v>
       </c>
     </row>
@@ -4876,12 +4446,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M87" t="n">
+      <c r="L87" t="n">
         <v>981</v>
       </c>
     </row>
@@ -4927,12 +4492,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M88" t="n">
+      <c r="L88" t="n">
         <v>1311</v>
       </c>
     </row>
@@ -4953,7 +4513,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -4978,12 +4538,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M89" t="n">
+      <c r="L89" t="n">
         <v>2763</v>
       </c>
     </row>
@@ -5004,7 +4559,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -5029,12 +4584,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M90" t="n">
+      <c r="L90" t="n">
         <v>981</v>
       </c>
     </row>
@@ -5055,7 +4605,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -5080,12 +4630,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M91" t="n">
+      <c r="L91" t="n">
         <v>2016</v>
       </c>
     </row>
@@ -5131,12 +4676,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M92" t="n">
+      <c r="L92" t="n">
         <v>319</v>
       </c>
     </row>
@@ -5182,12 +4722,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M93" t="n">
+      <c r="L93" t="n">
         <v>3364</v>
       </c>
     </row>
@@ -5208,7 +4743,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -5233,12 +4768,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M94" t="n">
+      <c r="L94" t="n">
         <v>2976</v>
       </c>
     </row>
@@ -5284,12 +4814,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M95" t="n">
+      <c r="L95" t="n">
         <v>2475</v>
       </c>
     </row>
@@ -5310,7 +4835,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -5335,12 +4860,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M96" t="n">
+      <c r="L96" t="n">
         <v>1167</v>
       </c>
     </row>
@@ -5361,7 +4881,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -5386,12 +4906,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M97" t="n">
+      <c r="L97" t="n">
         <v>1504</v>
       </c>
     </row>
@@ -5412,7 +4927,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -5437,12 +4952,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M98" t="n">
+      <c r="L98" t="n">
         <v>3968</v>
       </c>
     </row>
@@ -5463,7 +4973,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -5488,12 +4998,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M99" t="n">
+      <c r="L99" t="n">
         <v>1222</v>
       </c>
     </row>
@@ -5539,12 +5044,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M100" t="n">
+      <c r="L100" t="n">
         <v>282</v>
       </c>
     </row>
@@ -5590,12 +5090,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M101" t="n">
+      <c r="L101" t="n">
         <v>319</v>
       </c>
     </row>
@@ -5616,7 +5111,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -5641,12 +5136,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M102" t="n">
+      <c r="L102" t="n">
         <v>778</v>
       </c>
     </row>
@@ -5667,7 +5157,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -5692,12 +5182,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M103" t="n">
+      <c r="L103" t="n">
         <v>451</v>
       </c>
     </row>
@@ -5718,7 +5203,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -5743,12 +5228,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M104" t="n">
+      <c r="L104" t="n">
         <v>255</v>
       </c>
     </row>
@@ -5769,7 +5249,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -5794,12 +5274,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M105" t="n">
+      <c r="L105" t="n">
         <v>778</v>
       </c>
     </row>
@@ -5820,7 +5295,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -5845,12 +5320,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M106" t="n">
+      <c r="L106" t="n">
         <v>1276</v>
       </c>
     </row>
@@ -5871,7 +5341,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -5896,12 +5366,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M107" t="n">
+      <c r="L107" t="n">
         <v>3884</v>
       </c>
     </row>
@@ -5947,12 +5412,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M108" t="n">
+      <c r="L108" t="n">
         <v>408</v>
       </c>
     </row>
@@ -5973,7 +5433,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -5998,12 +5458,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M109" t="n">
+      <c r="L109" t="n">
         <v>3004</v>
       </c>
     </row>
@@ -6024,7 +5479,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -6049,12 +5504,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M110" t="n">
+      <c r="L110" t="n">
         <v>1748</v>
       </c>
     </row>
@@ -6075,7 +5525,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -6100,12 +5550,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M111" t="n">
+      <c r="L111" t="n">
         <v>1230</v>
       </c>
     </row>
@@ -6151,12 +5596,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M112" t="n">
+      <c r="L112" t="n">
         <v>778</v>
       </c>
     </row>
@@ -6202,12 +5642,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M113" t="n">
+      <c r="L113" t="n">
         <v>1185</v>
       </c>
     </row>
@@ -6228,7 +5663,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -6253,12 +5688,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M114" t="n">
+      <c r="L114" t="n">
         <v>2420</v>
       </c>
     </row>
@@ -6279,7 +5709,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -6304,12 +5734,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M115" t="n">
+      <c r="L115" t="n">
         <v>1856</v>
       </c>
     </row>
@@ -6355,12 +5780,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M116" t="n">
+      <c r="L116" t="n">
         <v>2328</v>
       </c>
     </row>
@@ -6406,12 +5826,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M117" t="n">
+      <c r="L117" t="n">
         <v>3788</v>
       </c>
     </row>
@@ -6432,7 +5847,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -6457,12 +5872,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M118" t="n">
+      <c r="L118" t="n">
         <v>319</v>
       </c>
     </row>
@@ -6483,7 +5893,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -6508,12 +5918,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M119" t="n">
+      <c r="L119" t="n">
         <v>252</v>
       </c>
     </row>
@@ -6534,7 +5939,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -6559,12 +5964,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M120" t="n">
+      <c r="L120" t="n">
         <v>102</v>
       </c>
     </row>
@@ -6585,7 +5985,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -6610,12 +6010,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M121" t="n">
+      <c r="L121" t="n">
         <v>416</v>
       </c>
     </row>
@@ -6636,7 +6031,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -6661,12 +6056,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M122" t="n">
+      <c r="L122" t="n">
         <v>130</v>
       </c>
     </row>
@@ -6687,7 +6077,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -6712,12 +6102,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M123" t="n">
+      <c r="L123" t="n">
         <v>155</v>
       </c>
     </row>
@@ -6738,7 +6123,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -6763,12 +6148,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M124" t="n">
+      <c r="L124" t="n">
         <v>765</v>
       </c>
     </row>
@@ -6789,7 +6169,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -6814,12 +6194,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M125" t="n">
+      <c r="L125" t="n">
         <v>310</v>
       </c>
     </row>
@@ -6865,12 +6240,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M126" t="n">
+      <c r="L126" t="n">
         <v>437</v>
       </c>
     </row>
@@ -6916,12 +6286,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M127" t="n">
+      <c r="L127" t="n">
         <v>3116</v>
       </c>
     </row>
@@ -6942,7 +6307,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -6967,12 +6332,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M128" t="n">
+      <c r="L128" t="n">
         <v>51</v>
       </c>
     </row>
@@ -7018,12 +6378,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M129" t="n">
+      <c r="L129" t="n">
         <v>779</v>
       </c>
     </row>
@@ -7069,12 +6424,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M130" t="n">
+      <c r="L130" t="n">
         <v>2463</v>
       </c>
     </row>
@@ -7095,7 +6445,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -7120,12 +6470,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M131" t="n">
+      <c r="L131" t="n">
         <v>2763</v>
       </c>
     </row>
@@ -7146,7 +6491,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -7171,12 +6516,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M132" t="n">
+      <c r="L132" t="n">
         <v>1116</v>
       </c>
     </row>
@@ -7197,7 +6537,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -7222,12 +6562,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M133" t="n">
+      <c r="L133" t="n">
         <v>3004</v>
       </c>
     </row>
@@ -7248,7 +6583,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -7273,12 +6608,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M134" t="n">
+      <c r="L134" t="n">
         <v>1512</v>
       </c>
     </row>
@@ -7324,12 +6654,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M135" t="n">
+      <c r="L135" t="n">
         <v>526</v>
       </c>
     </row>
@@ -7350,7 +6675,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -7375,12 +6700,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M136" t="n">
+      <c r="L136" t="n">
         <v>1558</v>
       </c>
     </row>
@@ -7401,7 +6721,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -7426,12 +6746,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M137" t="n">
+      <c r="L137" t="n">
         <v>558</v>
       </c>
     </row>
@@ -7452,7 +6767,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F138" t="n">
@@ -7477,12 +6792,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M138" t="n">
+      <c r="L138" t="n">
         <v>611</v>
       </c>
     </row>
@@ -7503,7 +6813,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F139" t="n">
@@ -7528,12 +6838,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M139" t="n">
+      <c r="L139" t="n">
         <v>1185</v>
       </c>
     </row>
@@ -7554,7 +6859,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -7579,12 +6884,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M140" t="n">
+      <c r="L140" t="n">
         <v>282</v>
       </c>
     </row>
@@ -7605,7 +6905,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -7630,12 +6930,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M141" t="n">
+      <c r="L141" t="n">
         <v>1556</v>
       </c>
     </row>
@@ -7656,7 +6951,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F142" t="n">
@@ -7681,12 +6976,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M142" t="n">
+      <c r="L142" t="n">
         <v>1804</v>
       </c>
     </row>
@@ -7732,12 +7022,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M143" t="n">
+      <c r="L143" t="n">
         <v>2253</v>
       </c>
     </row>
@@ -7758,7 +7043,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -7783,12 +7068,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M144" t="n">
+      <c r="L144" t="n">
         <v>1167</v>
       </c>
     </row>
@@ -7834,12 +7114,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M145" t="n">
+      <c r="L145" t="n">
         <v>1842</v>
       </c>
     </row>
@@ -7860,7 +7135,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -7885,12 +7160,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M146" t="n">
+      <c r="L146" t="n">
         <v>2104</v>
       </c>
     </row>
@@ -7911,7 +7181,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -7936,12 +7206,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M147" t="n">
+      <c r="L147" t="n">
         <v>204</v>
       </c>
     </row>
@@ -7962,7 +7227,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -7987,12 +7252,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M148" t="n">
+      <c r="L148" t="n">
         <v>3004</v>
       </c>
     </row>
@@ -8038,12 +7298,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M149" t="n">
+      <c r="L149" t="n">
         <v>841</v>
       </c>
     </row>
@@ -8064,7 +7319,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -8089,12 +7344,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M150" t="n">
+      <c r="L150" t="n">
         <v>3008</v>
       </c>
     </row>
@@ -8115,7 +7365,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -8140,12 +7390,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M151" t="n">
+      <c r="L151" t="n">
         <v>841</v>
       </c>
     </row>
@@ -8166,7 +7411,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -8191,12 +7436,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M152" t="n">
+      <c r="L152" t="n">
         <v>1984</v>
       </c>
     </row>
@@ -8217,7 +7457,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -8242,12 +7482,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M153" t="n">
+      <c r="L153" t="n">
         <v>416</v>
       </c>
     </row>
@@ -8293,12 +7528,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M154" t="n">
+      <c r="L154" t="n">
         <v>1228</v>
       </c>
     </row>
@@ -8319,7 +7549,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -8344,12 +7574,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M155" t="n">
+      <c r="L155" t="n">
         <v>2232</v>
       </c>
     </row>
@@ -8370,7 +7595,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -8395,12 +7620,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M156" t="n">
+      <c r="L156" t="n">
         <v>3648</v>
       </c>
     </row>
@@ -8421,7 +7641,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -8446,12 +7666,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M157" t="n">
+      <c r="L157" t="n">
         <v>1742</v>
       </c>
     </row>
@@ -8497,12 +7712,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M158" t="n">
+      <c r="L158" t="n">
         <v>2595</v>
       </c>
     </row>
@@ -8548,12 +7758,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M159" t="n">
+      <c r="L159" t="n">
         <v>1962</v>
       </c>
     </row>
@@ -8574,7 +7779,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -8599,12 +7804,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M160" t="n">
+      <c r="L160" t="n">
         <v>1185</v>
       </c>
     </row>
@@ -8650,12 +7850,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M161" t="n">
+      <c r="L161" t="n">
         <v>821</v>
       </c>
     </row>
@@ -8676,7 +7871,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -8701,12 +7896,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M162" t="n">
+      <c r="L162" t="n">
         <v>558</v>
       </c>
     </row>
@@ -8752,12 +7942,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M163" t="n">
+      <c r="L163" t="n">
         <v>511</v>
       </c>
     </row>
@@ -8778,7 +7963,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -8803,12 +7988,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M164" t="n">
+      <c r="L164" t="n">
         <v>2460</v>
       </c>
     </row>
@@ -8854,12 +8034,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M165" t="n">
+      <c r="L165" t="n">
         <v>526</v>
       </c>
     </row>
@@ -8880,7 +8055,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -8905,12 +8080,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M166" t="n">
+      <c r="L166" t="n">
         <v>2322</v>
       </c>
     </row>
@@ -8931,7 +8101,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F167" t="n">
@@ -8956,12 +8126,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M167" t="n">
+      <c r="L167" t="n">
         <v>776</v>
       </c>
     </row>
@@ -9007,12 +8172,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M168" t="n">
+      <c r="L168" t="n">
         <v>1504</v>
       </c>
     </row>
@@ -9058,12 +8218,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M169" t="n">
+      <c r="L169" t="n">
         <v>1558</v>
       </c>
     </row>
@@ -9109,12 +8264,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M170" t="n">
+      <c r="L170" t="n">
         <v>3712</v>
       </c>
     </row>
@@ -9135,7 +8285,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -9160,12 +8310,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M171" t="n">
+      <c r="L171" t="n">
         <v>1022</v>
       </c>
     </row>
@@ -9186,7 +8331,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -9211,12 +8356,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M172" t="n">
+      <c r="L172" t="n">
         <v>153</v>
       </c>
     </row>
@@ -9237,7 +8377,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -9262,12 +8402,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L173" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M173" t="n">
+      <c r="L173" t="n">
         <v>752</v>
       </c>
     </row>
@@ -9288,7 +8423,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -9313,12 +8448,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M174" t="n">
+      <c r="L174" t="n">
         <v>3004</v>
       </c>
     </row>
@@ -9364,12 +8494,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M175" t="n">
+      <c r="L175" t="n">
         <v>51</v>
       </c>
     </row>
@@ -9415,12 +8540,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M176" t="n">
+      <c r="L176" t="n">
         <v>769</v>
       </c>
     </row>
@@ -9441,7 +8561,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -9466,12 +8586,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M177" t="n">
+      <c r="L177" t="n">
         <v>1311</v>
       </c>
     </row>
@@ -9517,12 +8632,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M178" t="n">
+      <c r="L178" t="n">
         <v>102</v>
       </c>
     </row>
@@ -9543,7 +8653,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -9568,12 +8678,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M179" t="n">
+      <c r="L179" t="n">
         <v>1730</v>
       </c>
     </row>
@@ -9619,12 +8724,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M180" t="n">
+      <c r="L180" t="n">
         <v>928</v>
       </c>
     </row>
@@ -9670,12 +8770,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M181" t="n">
+      <c r="L181" t="n">
         <v>1580</v>
       </c>
     </row>
@@ -9696,7 +8791,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -9721,12 +8816,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M182" t="n">
+      <c r="L182" t="n">
         <v>1210</v>
       </c>
     </row>
@@ -9772,12 +8862,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L183" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M183" t="n">
+      <c r="L183" t="n">
         <v>3648</v>
       </c>
     </row>
@@ -9798,7 +8883,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -9823,12 +8908,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M184" t="n">
+      <c r="L184" t="n">
         <v>1230</v>
       </c>
     </row>
@@ -9849,7 +8929,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -9874,12 +8954,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L185" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M185" t="n">
+      <c r="L185" t="n">
         <v>2456</v>
       </c>
     </row>
@@ -9925,12 +9000,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L186" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M186" t="n">
+      <c r="L186" t="n">
         <v>423</v>
       </c>
     </row>
@@ -9951,7 +9021,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -9976,12 +9046,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M187" t="n">
+      <c r="L187" t="n">
         <v>520</v>
       </c>
     </row>
@@ -10002,7 +9067,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -10027,12 +9092,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M188" t="n">
+      <c r="L188" t="n">
         <v>2256</v>
       </c>
     </row>
@@ -10078,12 +9138,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L189" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M189" t="n">
+      <c r="L189" t="n">
         <v>1674</v>
       </c>
     </row>
@@ -10104,7 +9159,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -10129,12 +9184,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L190" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M190" t="n">
+      <c r="L190" t="n">
         <v>1908</v>
       </c>
     </row>
@@ -10180,12 +9230,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L191" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M191" t="n">
+      <c r="L191" t="n">
         <v>957</v>
       </c>
     </row>
@@ -10206,7 +9251,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F192" t="n">
@@ -10231,12 +9276,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L192" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M192" t="n">
+      <c r="L192" t="n">
         <v>251</v>
       </c>
     </row>
@@ -10257,7 +9297,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -10282,12 +9322,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M193" t="n">
+      <c r="L193" t="n">
         <v>306</v>
       </c>
     </row>
@@ -10308,7 +9343,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -10333,12 +9368,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L194" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M194" t="n">
+      <c r="L194" t="n">
         <v>282</v>
       </c>
     </row>
@@ -10359,7 +9389,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F195" t="n">
@@ -10384,12 +9414,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M195" t="n">
+      <c r="L195" t="n">
         <v>3004</v>
       </c>
     </row>
@@ -10410,7 +9435,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F196" t="n">
@@ -10435,12 +9460,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L196" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M196" t="n">
+      <c r="L196" t="n">
         <v>320</v>
       </c>
     </row>
@@ -10461,7 +9481,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -10486,12 +9506,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L197" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M197" t="n">
+      <c r="L197" t="n">
         <v>1580</v>
       </c>
     </row>
@@ -10512,7 +9527,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -10537,12 +9552,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M198" t="n">
+      <c r="L198" t="n">
         <v>1558</v>
       </c>
     </row>
@@ -10563,7 +9573,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F199" t="n">
@@ -10588,12 +9598,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L199" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M199" t="n">
+      <c r="L199" t="n">
         <v>1894</v>
       </c>
     </row>
@@ -10614,7 +9619,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -10639,12 +9644,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L200" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M200" t="n">
+      <c r="L200" t="n">
         <v>1652</v>
       </c>
     </row>
@@ -10665,7 +9665,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -10690,12 +9690,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L201" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M201" t="n">
+      <c r="L201" t="n">
         <v>1311</v>
       </c>
     </row>
@@ -10716,7 +9711,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -10741,12 +9736,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L202" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M202" t="n">
+      <c r="L202" t="n">
         <v>1578</v>
       </c>
     </row>
@@ -10792,12 +9782,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L203" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M203" t="n">
+      <c r="L203" t="n">
         <v>3484</v>
       </c>
     </row>
@@ -10818,7 +9803,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -10843,12 +9828,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L204" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M204" t="n">
+      <c r="L204" t="n">
         <v>2232</v>
       </c>
     </row>
@@ -10869,7 +9849,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F205" t="n">
@@ -10894,12 +9874,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L205" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M205" t="n">
+      <c r="L205" t="n">
         <v>130</v>
       </c>
     </row>
@@ -10920,7 +9895,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F206" t="n">
@@ -10945,12 +9920,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M206" t="n">
+      <c r="L206" t="n">
         <v>615</v>
       </c>
     </row>
@@ -10996,12 +9966,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L207" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M207" t="n">
+      <c r="L207" t="n">
         <v>408</v>
       </c>
     </row>
@@ -11047,12 +10012,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L208" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M208" t="n">
+      <c r="L208" t="n">
         <v>1317</v>
       </c>
     </row>
@@ -11098,12 +10058,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L209" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M209" t="n">
+      <c r="L209" t="n">
         <v>1230</v>
       </c>
     </row>
@@ -11124,7 +10079,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F210" t="n">
@@ -11149,12 +10104,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M210" t="n">
+      <c r="L210" t="n">
         <v>1280</v>
       </c>
     </row>
@@ -11175,7 +10125,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F211" t="n">
@@ -11200,12 +10150,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M211" t="n">
+      <c r="L211" t="n">
         <v>912</v>
       </c>
     </row>
@@ -11251,12 +10196,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L212" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M212" t="n">
+      <c r="L212" t="n">
         <v>1815</v>
       </c>
     </row>
@@ -11302,12 +10242,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L213" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M213" t="n">
+      <c r="L213" t="n">
         <v>3484</v>
       </c>
     </row>
@@ -11328,7 +10263,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F214" t="n">
@@ -11353,12 +10288,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L214" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M214" t="n">
+      <c r="L214" t="n">
         <v>3192</v>
       </c>
     </row>
@@ -11379,7 +10309,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F215" t="n">
@@ -11404,12 +10334,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L215" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M215" t="n">
+      <c r="L215" t="n">
         <v>1353</v>
       </c>
     </row>
@@ -11455,12 +10380,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L216" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M216" t="n">
+      <c r="L216" t="n">
         <v>3304</v>
       </c>
     </row>
@@ -11481,7 +10401,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F217" t="n">
@@ -11506,12 +10426,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L217" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M217" t="n">
+      <c r="L217" t="n">
         <v>2523</v>
       </c>
     </row>
@@ -11532,7 +10447,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F218" t="n">
@@ -11557,12 +10472,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L218" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M218" t="n">
+      <c r="L218" t="n">
         <v>1596</v>
       </c>
     </row>
@@ -11608,12 +10518,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L219" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M219" t="n">
+      <c r="L219" t="n">
         <v>2841</v>
       </c>
     </row>
@@ -11659,12 +10564,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L220" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M220" t="n">
+      <c r="L220" t="n">
         <v>1248</v>
       </c>
     </row>
@@ -11710,12 +10610,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L221" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M221" t="n">
+      <c r="L221" t="n">
         <v>2523</v>
       </c>
     </row>
@@ -11736,7 +10631,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F222" t="n">
@@ -11761,12 +10656,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L222" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M222" t="n">
+      <c r="L222" t="n">
         <v>1908</v>
       </c>
     </row>
@@ -11812,12 +10702,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L223" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M223" t="n">
+      <c r="L223" t="n">
         <v>1280</v>
       </c>
     </row>
@@ -11863,12 +10748,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L224" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M224" t="n">
+      <c r="L224" t="n">
         <v>1311</v>
       </c>
     </row>
@@ -11889,7 +10769,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F225" t="n">
@@ -11914,12 +10794,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L225" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M225" t="n">
+      <c r="L225" t="n">
         <v>3304</v>
       </c>
     </row>
@@ -11940,7 +10815,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F226" t="n">
@@ -11965,12 +10840,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L226" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M226" t="n">
+      <c r="L226" t="n">
         <v>558</v>
       </c>
     </row>
@@ -12016,12 +10886,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L227" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M227" t="n">
+      <c r="L227" t="n">
         <v>320</v>
       </c>
     </row>
@@ -12042,7 +10907,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F228" t="n">
@@ -12067,12 +10932,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L228" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M228" t="n">
+      <c r="L228" t="n">
         <v>1908</v>
       </c>
     </row>
@@ -12093,7 +10953,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F229" t="n">
@@ -12118,12 +10978,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L229" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M229" t="n">
+      <c r="L229" t="n">
         <v>3192</v>
       </c>
     </row>
@@ -12144,7 +10999,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F230" t="n">
@@ -12169,12 +11024,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L230" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M230" t="n">
+      <c r="L230" t="n">
         <v>1161</v>
       </c>
     </row>
@@ -12220,12 +11070,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L231" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M231" t="n">
+      <c r="L231" t="n">
         <v>690</v>
       </c>
     </row>
@@ -12246,7 +11091,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F232" t="n">
@@ -12271,12 +11116,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L232" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M232" t="n">
+      <c r="L232" t="n">
         <v>1004</v>
       </c>
     </row>
@@ -12322,12 +11162,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L233" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M233" t="n">
+      <c r="L233" t="n">
         <v>251</v>
       </c>
     </row>
@@ -12348,7 +11183,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F234" t="n">
@@ -12373,12 +11208,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L234" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M234" t="n">
+      <c r="L234" t="n">
         <v>423</v>
       </c>
     </row>
@@ -12399,7 +11229,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F235" t="n">
@@ -12424,12 +11254,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L235" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M235" t="n">
+      <c r="L235" t="n">
         <v>408</v>
       </c>
     </row>
@@ -12450,7 +11275,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F236" t="n">
@@ -12475,12 +11300,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L236" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M236" t="n">
+      <c r="L236" t="n">
         <v>511</v>
       </c>
     </row>
@@ -12526,12 +11346,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L237" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M237" t="n">
+      <c r="L237" t="n">
         <v>611</v>
       </c>
     </row>
@@ -12577,12 +11392,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L238" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M238" t="n">
+      <c r="L238" t="n">
         <v>1116</v>
       </c>
     </row>
@@ -12603,7 +11413,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F239" t="n">
@@ -12628,12 +11438,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L239" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M239" t="n">
+      <c r="L239" t="n">
         <v>2913</v>
       </c>
     </row>
@@ -12679,12 +11484,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L240" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M240" t="n">
+      <c r="L240" t="n">
         <v>2256</v>
       </c>
     </row>
@@ -12705,7 +11505,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F241" t="n">
@@ -12730,12 +11530,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L241" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M241" t="n">
+      <c r="L241" t="n">
         <v>1942</v>
       </c>
     </row>
@@ -12756,7 +11551,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F242" t="n">
@@ -12781,12 +11576,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L242" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M242" t="n">
+      <c r="L242" t="n">
         <v>1730</v>
       </c>
     </row>
@@ -12807,7 +11597,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F243" t="n">
@@ -12832,12 +11622,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L243" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M243" t="n">
+      <c r="L243" t="n">
         <v>1317</v>
       </c>
     </row>
@@ -12858,7 +11643,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F244" t="n">
@@ -12883,12 +11668,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L244" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M244" t="n">
+      <c r="L244" t="n">
         <v>2613</v>
       </c>
     </row>
@@ -12934,12 +11714,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L245" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M245" t="n">
+      <c r="L245" t="n">
         <v>1804</v>
       </c>
     </row>
@@ -12985,12 +11760,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L246" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M246" t="n">
+      <c r="L246" t="n">
         <v>3712</v>
       </c>
     </row>
@@ -13011,7 +11781,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -13036,12 +11806,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L247" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M247" t="n">
+      <c r="L247" t="n">
         <v>260</v>
       </c>
     </row>
@@ -13087,12 +11852,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L248" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M248" t="n">
+      <c r="L248" t="n">
         <v>3788</v>
       </c>
     </row>
@@ -13113,7 +11873,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -13138,12 +11898,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L249" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M249" t="n">
+      <c r="L249" t="n">
         <v>779</v>
       </c>
     </row>
@@ -13189,12 +11944,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L250" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M250" t="n">
+      <c r="L250" t="n">
         <v>1908</v>
       </c>
     </row>
@@ -13215,7 +11965,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F251" t="n">
@@ -13240,12 +11990,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L251" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M251" t="n">
+      <c r="L251" t="n">
         <v>3008</v>
       </c>
     </row>
@@ -13266,7 +12011,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -13291,12 +12036,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L252" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M252" t="n">
+      <c r="L252" t="n">
         <v>526</v>
       </c>
     </row>
@@ -13342,12 +12082,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L253" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M253" t="n">
+      <c r="L253" t="n">
         <v>874</v>
       </c>
     </row>
@@ -13393,12 +12128,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L254" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M254" t="n">
+      <c r="L254" t="n">
         <v>451</v>
       </c>
     </row>
@@ -13419,7 +12149,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F255" t="n">
@@ -13444,12 +12174,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L255" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M255" t="n">
+      <c r="L255" t="n">
         <v>2444</v>
       </c>
     </row>
@@ -13470,7 +12195,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F256" t="n">
@@ -13495,12 +12220,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L256" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M256" t="n">
+      <c r="L256" t="n">
         <v>1548</v>
       </c>
     </row>
@@ -13521,7 +12241,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F257" t="n">
@@ -13546,12 +12266,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L257" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M257" t="n">
+      <c r="L257" t="n">
         <v>3004</v>
       </c>
     </row>
@@ -13597,12 +12312,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L258" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M258" t="n">
+      <c r="L258" t="n">
         <v>345</v>
       </c>
     </row>
@@ -13623,7 +12333,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -13648,12 +12358,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L259" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M259" t="n">
+      <c r="L259" t="n">
         <v>971</v>
       </c>
     </row>
@@ -13674,7 +12379,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F260" t="n">
@@ -13699,12 +12404,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L260" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M260" t="n">
+      <c r="L260" t="n">
         <v>204</v>
       </c>
     </row>
@@ -13725,7 +12425,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F261" t="n">
@@ -13750,12 +12450,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L261" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M261" t="n">
+      <c r="L261" t="n">
         <v>2394</v>
       </c>
     </row>
@@ -13801,12 +12496,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L262" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M262" t="n">
+      <c r="L262" t="n">
         <v>903</v>
       </c>
     </row>
@@ -13827,7 +12517,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F263" t="n">
@@ -13852,12 +12542,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L263" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M263" t="n">
+      <c r="L263" t="n">
         <v>776</v>
       </c>
     </row>
@@ -13878,7 +12563,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F264" t="n">
@@ -13903,12 +12588,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L264" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M264" t="n">
+      <c r="L264" t="n">
         <v>841</v>
       </c>
     </row>
@@ -13954,12 +12634,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L265" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M265" t="n">
+      <c r="L265" t="n">
         <v>465</v>
       </c>
     </row>
@@ -14005,12 +12680,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L266" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M266" t="n">
+      <c r="L266" t="n">
         <v>2784</v>
       </c>
     </row>
@@ -14056,12 +12726,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L267" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M267" t="n">
+      <c r="L267" t="n">
         <v>1004</v>
       </c>
     </row>
@@ -14082,7 +12747,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F268" t="n">
@@ -14107,12 +12772,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L268" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M268" t="n">
+      <c r="L268" t="n">
         <v>3712</v>
       </c>
     </row>
@@ -14133,7 +12793,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F269" t="n">
@@ -14158,12 +12818,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L269" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M269" t="n">
+      <c r="L269" t="n">
         <v>957</v>
       </c>
     </row>
@@ -14209,12 +12864,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L270" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M270" t="n">
+      <c r="L270" t="n">
         <v>1548</v>
       </c>
     </row>
@@ -14235,7 +12885,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F271" t="n">
@@ -14260,12 +12910,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L271" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M271" t="n">
+      <c r="L271" t="n">
         <v>1556</v>
       </c>
     </row>
@@ -14311,12 +12956,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L272" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M272" t="n">
+      <c r="L272" t="n">
         <v>1548</v>
       </c>
     </row>
@@ -14337,7 +12977,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -14362,12 +13002,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L273" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M273" t="n">
+      <c r="L273" t="n">
         <v>408</v>
       </c>
     </row>
@@ -14388,7 +13023,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F274" t="n">
@@ -14413,12 +13048,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L274" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M274" t="n">
+      <c r="L274" t="n">
         <v>912</v>
       </c>
     </row>
@@ -14464,12 +13094,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L275" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M275" t="n">
+      <c r="L275" t="n">
         <v>1204</v>
       </c>
     </row>
@@ -14490,7 +13115,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F276" t="n">
@@ -14515,12 +13140,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L276" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M276" t="n">
+      <c r="L276" t="n">
         <v>3300</v>
       </c>
     </row>
@@ -14566,12 +13186,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L277" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M277" t="n">
+      <c r="L277" t="n">
         <v>2913</v>
       </c>
     </row>
@@ -14592,7 +13207,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F278" t="n">
@@ -14617,12 +13232,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L278" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M278" t="n">
+      <c r="L278" t="n">
         <v>614</v>
       </c>
     </row>
@@ -14668,12 +13278,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L279" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M279" t="n">
+      <c r="L279" t="n">
         <v>1276</v>
       </c>
     </row>
@@ -14694,7 +13299,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -14719,12 +13324,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L280" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M280" t="n">
+      <c r="L280" t="n">
         <v>3300</v>
       </c>
     </row>
@@ -14770,12 +13370,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L281" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M281" t="n">
+      <c r="L281" t="n">
         <v>1962</v>
       </c>
     </row>
@@ -14796,7 +13391,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -14821,12 +13416,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L282" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M282" t="n">
+      <c r="L282" t="n">
         <v>3684</v>
       </c>
     </row>
@@ -14847,7 +13437,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -14872,12 +13462,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L283" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M283" t="n">
+      <c r="L283" t="n">
         <v>2420</v>
       </c>
     </row>
@@ -14898,7 +13483,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -14923,12 +13508,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L284" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M284" t="n">
+      <c r="L284" t="n">
         <v>204</v>
       </c>
     </row>
@@ -14949,7 +13529,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F285" t="n">
@@ -14974,12 +13554,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L285" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M285" t="n">
+      <c r="L285" t="n">
         <v>1674</v>
       </c>
     </row>
@@ -15000,7 +13575,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F286" t="n">
@@ -15025,12 +13600,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L286" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M286" t="n">
+      <c r="L286" t="n">
         <v>3684</v>
       </c>
     </row>
@@ -15051,7 +13621,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F287" t="n">
@@ -15076,12 +13646,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L287" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M287" t="n">
+      <c r="L287" t="n">
         <v>1022</v>
       </c>
     </row>
@@ -15127,12 +13692,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L288" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M288" t="n">
+      <c r="L288" t="n">
         <v>437</v>
       </c>
     </row>
@@ -15153,7 +13713,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F289" t="n">
@@ -15178,12 +13738,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L289" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M289" t="n">
+      <c r="L289" t="n">
         <v>960</v>
       </c>
     </row>
@@ -15204,7 +13759,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F290" t="n">
@@ -15229,12 +13784,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L290" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M290" t="n">
+      <c r="L290" t="n">
         <v>84</v>
       </c>
     </row>
@@ -15255,7 +13805,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F291" t="n">
@@ -15280,12 +13830,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L291" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M291" t="n">
+      <c r="L291" t="n">
         <v>387</v>
       </c>
     </row>
@@ -15331,12 +13876,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L292" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M292" t="n">
+      <c r="L292" t="n">
         <v>1228</v>
       </c>
     </row>
@@ -15357,7 +13897,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F293" t="n">
@@ -15382,12 +13922,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L293" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M293" t="n">
+      <c r="L293" t="n">
         <v>2232</v>
       </c>
     </row>
@@ -15433,12 +13968,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L294" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M294" t="n">
+      <c r="L294" t="n">
         <v>1022</v>
       </c>
     </row>
@@ -15484,12 +14014,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L295" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M295" t="n">
+      <c r="L295" t="n">
         <v>1652</v>
       </c>
     </row>
@@ -15510,7 +14035,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F296" t="n">
@@ -15535,12 +14060,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L296" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M296" t="n">
+      <c r="L296" t="n">
         <v>1504</v>
       </c>
     </row>
@@ -15561,7 +14081,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F297" t="n">
@@ -15586,12 +14106,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L297" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M297" t="n">
+      <c r="L297" t="n">
         <v>774</v>
       </c>
     </row>
@@ -15637,12 +14152,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L298" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M298" t="n">
+      <c r="L298" t="n">
         <v>1512</v>
       </c>
     </row>
@@ -15688,12 +14198,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L299" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M299" t="n">
+      <c r="L299" t="n">
         <v>1548</v>
       </c>
     </row>
@@ -15714,7 +14219,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F300" t="n">
@@ -15739,12 +14244,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L300" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M300" t="n">
+      <c r="L300" t="n">
         <v>345</v>
       </c>
     </row>
@@ -15765,7 +14265,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F301" t="n">
@@ -15790,12 +14290,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L301" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M301" t="n">
+      <c r="L301" t="n">
         <v>611</v>
       </c>
     </row>
@@ -15816,7 +14311,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F302" t="n">
@@ -15841,12 +14336,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L302" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M302" t="n">
+      <c r="L302" t="n">
         <v>1908</v>
       </c>
     </row>
@@ -15867,7 +14357,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F303" t="n">
@@ -15892,12 +14382,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L303" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M303" t="n">
+      <c r="L303" t="n">
         <v>141</v>
       </c>
     </row>
@@ -15943,12 +14428,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L304" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M304" t="n">
+      <c r="L304" t="n">
         <v>3096</v>
       </c>
     </row>
@@ -15969,7 +14449,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F305" t="n">
@@ -15994,12 +14474,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L305" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M305" t="n">
+      <c r="L305" t="n">
         <v>871</v>
       </c>
     </row>
@@ -16020,7 +14495,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F306" t="n">
@@ -16045,12 +14520,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L306" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M306" t="n">
+      <c r="L306" t="n">
         <v>1552</v>
       </c>
     </row>
@@ -16071,7 +14541,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F307" t="n">
@@ -16096,12 +14566,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L307" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M307" t="n">
+      <c r="L307" t="n">
         <v>841</v>
       </c>
     </row>
@@ -16122,7 +14587,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F308" t="n">
@@ -16147,12 +14612,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L308" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M308" t="n">
+      <c r="L308" t="n">
         <v>1804</v>
       </c>
     </row>
@@ -16173,7 +14633,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -16198,12 +14658,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L309" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M309" t="n">
+      <c r="L309" t="n">
         <v>1276</v>
       </c>
     </row>
@@ -16249,12 +14704,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L310" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M310" t="n">
+      <c r="L310" t="n">
         <v>2020</v>
       </c>
     </row>
@@ -16275,7 +14725,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -16300,12 +14750,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L311" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M311" t="n">
+      <c r="L311" t="n">
         <v>1908</v>
       </c>
     </row>
@@ -16351,12 +14796,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L312" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M312" t="n">
+      <c r="L312" t="n">
         <v>3684</v>
       </c>
     </row>
@@ -16377,7 +14817,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F313" t="n">
@@ -16402,12 +14842,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L313" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M313" t="n">
+      <c r="L313" t="n">
         <v>1317</v>
       </c>
     </row>
@@ -16428,7 +14863,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -16453,12 +14888,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L314" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M314" t="n">
+      <c r="L314" t="n">
         <v>1185</v>
       </c>
     </row>
@@ -16479,7 +14909,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -16504,12 +14934,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L315" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M315" t="n">
+      <c r="L315" t="n">
         <v>774</v>
       </c>
     </row>
@@ -16530,7 +14955,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -16555,12 +14980,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L316" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M316" t="n">
+      <c r="L316" t="n">
         <v>2044</v>
       </c>
     </row>
@@ -16581,7 +15001,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -16606,12 +15026,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L317" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M317" t="n">
+      <c r="L317" t="n">
         <v>301</v>
       </c>
     </row>
@@ -16632,7 +15047,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -16657,12 +15072,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L318" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M318" t="n">
+      <c r="L318" t="n">
         <v>1280</v>
       </c>
     </row>
@@ -16683,7 +15093,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -16708,12 +15118,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L319" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M319" t="n">
+      <c r="L319" t="n">
         <v>3884</v>
       </c>
     </row>
@@ -16759,12 +15164,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L320" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M320" t="n">
+      <c r="L320" t="n">
         <v>2322</v>
       </c>
     </row>
@@ -16785,7 +15185,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F321" t="n">
@@ -16810,12 +15210,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L321" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M321" t="n">
+      <c r="L321" t="n">
         <v>1515</v>
       </c>
     </row>
@@ -16861,12 +15256,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L322" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M322" t="n">
+      <c r="L322" t="n">
         <v>260</v>
       </c>
     </row>
@@ -16887,7 +15277,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F323" t="n">
@@ -16912,12 +15302,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L323" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M323" t="n">
+      <c r="L323" t="n">
         <v>1353</v>
       </c>
     </row>
@@ -16938,7 +15323,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F324" t="n">
@@ -16963,12 +15348,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L324" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M324" t="n">
+      <c r="L324" t="n">
         <v>1842</v>
       </c>
     </row>
@@ -16989,7 +15369,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F325" t="n">
@@ -17014,12 +15394,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L325" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M325" t="n">
+      <c r="L325" t="n">
         <v>1824</v>
       </c>
     </row>
@@ -17065,12 +15440,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L326" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M326" t="n">
+      <c r="L326" t="n">
         <v>1230</v>
       </c>
     </row>
@@ -17091,7 +15461,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -17116,12 +15486,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L327" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M327" t="n">
+      <c r="L327" t="n">
         <v>1650</v>
       </c>
     </row>
@@ -17142,7 +15507,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -17167,12 +15532,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L328" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M328" t="n">
+      <c r="L328" t="n">
         <v>168</v>
       </c>
     </row>
@@ -17193,7 +15553,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -17218,12 +15578,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L329" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M329" t="n">
+      <c r="L329" t="n">
         <v>947</v>
       </c>
     </row>
@@ -17244,7 +15599,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -17269,12 +15624,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L330" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M330" t="n">
+      <c r="L330" t="n">
         <v>1845</v>
       </c>
     </row>
@@ -17295,7 +15645,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F331" t="n">
@@ -17320,12 +15670,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L331" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M331" t="n">
+      <c r="L331" t="n">
         <v>832</v>
       </c>
     </row>
@@ -17346,7 +15691,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -17371,12 +15716,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L332" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M332" t="n">
+      <c r="L332" t="n">
         <v>3096</v>
       </c>
     </row>
@@ -17397,7 +15737,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -17422,12 +15762,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L333" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M333" t="n">
+      <c r="L333" t="n">
         <v>2463</v>
       </c>
     </row>
@@ -17448,7 +15783,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -17473,12 +15808,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L334" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M334" t="n">
+      <c r="L334" t="n">
         <v>2841</v>
       </c>
     </row>
@@ -17524,12 +15854,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L335" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M335" t="n">
+      <c r="L335" t="n">
         <v>902</v>
       </c>
     </row>
@@ -17575,12 +15900,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L336" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M336" t="n">
+      <c r="L336" t="n">
         <v>130</v>
       </c>
     </row>
@@ -17601,7 +15921,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F337" t="n">
@@ -17626,12 +15946,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L337" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M337" t="n">
+      <c r="L337" t="n">
         <v>1652</v>
       </c>
     </row>
@@ -17652,7 +15967,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F338" t="n">
@@ -17677,12 +15992,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L338" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M338" t="n">
+      <c r="L338" t="n">
         <v>614</v>
       </c>
     </row>
@@ -17703,7 +16013,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F339" t="n">
@@ -17728,12 +16038,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L339" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M339" t="n">
+      <c r="L339" t="n">
         <v>1020</v>
       </c>
     </row>
@@ -17779,12 +16084,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L340" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M340" t="n">
+      <c r="L340" t="n">
         <v>1533</v>
       </c>
     </row>
@@ -17805,7 +16105,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -17830,12 +16130,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L341" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M341" t="n">
+      <c r="L341" t="n">
         <v>3884</v>
       </c>
     </row>
@@ -17856,7 +16151,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F342" t="n">
@@ -17881,12 +16176,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L342" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M342" t="n">
+      <c r="L342" t="n">
         <v>826</v>
       </c>
     </row>
@@ -17907,7 +16197,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F343" t="n">
@@ -17932,12 +16222,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L343" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M343" t="n">
+      <c r="L343" t="n">
         <v>511</v>
       </c>
     </row>
@@ -17958,7 +16243,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F344" t="n">
@@ -17983,12 +16268,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L344" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M344" t="n">
+      <c r="L344" t="n">
         <v>2044</v>
       </c>
     </row>
@@ -18009,7 +16289,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -18034,12 +16314,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L345" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M345" t="n">
+      <c r="L345" t="n">
         <v>439</v>
       </c>
     </row>
@@ -18085,12 +16360,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L346" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M346" t="n">
+      <c r="L346" t="n">
         <v>408</v>
       </c>
     </row>
@@ -18111,7 +16381,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F347" t="n">
@@ -18136,12 +16406,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L347" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M347" t="n">
+      <c r="L347" t="n">
         <v>2337</v>
       </c>
     </row>
@@ -18162,7 +16427,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F348" t="n">
@@ -18187,12 +16452,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L348" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M348" t="n">
+      <c r="L348" t="n">
         <v>1556</v>
       </c>
     </row>
@@ -18213,7 +16473,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F349" t="n">
@@ -18238,12 +16498,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L349" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M349" t="n">
+      <c r="L349" t="n">
         <v>2523</v>
       </c>
     </row>
@@ -18264,7 +16519,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F350" t="n">
@@ -18289,12 +16544,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L350" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M350" t="n">
+      <c r="L350" t="n">
         <v>2232</v>
       </c>
     </row>
@@ -18315,7 +16565,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F351" t="n">
@@ -18340,12 +16590,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L351" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M351" t="n">
+      <c r="L351" t="n">
         <v>451</v>
       </c>
     </row>
@@ -18391,12 +16636,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L352" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M352" t="n">
+      <c r="L352" t="n">
         <v>1756</v>
       </c>
     </row>
@@ -18417,7 +16657,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F353" t="n">
@@ -18442,12 +16682,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L353" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M353" t="n">
+      <c r="L353" t="n">
         <v>971</v>
       </c>
     </row>
@@ -18468,7 +16703,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F354" t="n">
@@ -18493,12 +16728,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L354" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M354" t="n">
+      <c r="L354" t="n">
         <v>1664</v>
       </c>
     </row>
@@ -18544,12 +16774,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L355" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M355" t="n">
+      <c r="L355" t="n">
         <v>2456</v>
       </c>
     </row>
@@ -18570,7 +16795,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F356" t="n">
@@ -18595,12 +16820,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L356" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M356" t="n">
+      <c r="L356" t="n">
         <v>1596</v>
       </c>
     </row>
@@ -18621,7 +16841,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F357" t="n">
@@ -18646,12 +16866,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L357" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M357" t="n">
+      <c r="L357" t="n">
         <v>928</v>
       </c>
     </row>
@@ -18697,12 +16912,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L358" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M358" t="n">
+      <c r="L358" t="n">
         <v>102</v>
       </c>
     </row>
@@ -18723,7 +16933,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F359" t="n">
@@ -18748,12 +16958,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L359" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M359" t="n">
+      <c r="L359" t="n">
         <v>437</v>
       </c>
     </row>
@@ -18799,12 +17004,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L360" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M360" t="n">
+      <c r="L360" t="n">
         <v>1730</v>
       </c>
     </row>
@@ -18825,7 +17025,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F361" t="n">
@@ -18850,12 +17050,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L361" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M361" t="n">
+      <c r="L361" t="n">
         <v>2841</v>
       </c>
     </row>
@@ -18876,7 +17071,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F362" t="n">
@@ -18901,12 +17096,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L362" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M362" t="n">
+      <c r="L362" t="n">
         <v>1556</v>
       </c>
     </row>
@@ -18952,12 +17142,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L363" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M363" t="n">
+      <c r="L363" t="n">
         <v>826</v>
       </c>
     </row>
@@ -19003,12 +17188,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L364" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M364" t="n">
+      <c r="L364" t="n">
         <v>947</v>
       </c>
     </row>
@@ -19054,12 +17234,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L365" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M365" t="n">
+      <c r="L365" t="n">
         <v>3968</v>
       </c>
     </row>
@@ -19080,7 +17255,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F366" t="n">
@@ -19105,12 +17280,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L366" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M366" t="n">
+      <c r="L366" t="n">
         <v>752</v>
       </c>
     </row>
@@ -19131,7 +17301,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F367" t="n">
@@ -19156,12 +17326,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L367" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M367" t="n">
+      <c r="L367" t="n">
         <v>345</v>
       </c>
     </row>
@@ -19207,12 +17372,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L368" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M368" t="n">
+      <c r="L368" t="n">
         <v>310</v>
       </c>
     </row>
@@ -19233,7 +17393,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F369" t="n">
@@ -19258,12 +17418,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L369" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M369" t="n">
+      <c r="L369" t="n">
         <v>871</v>
       </c>
     </row>
@@ -19309,12 +17464,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L370" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M370" t="n">
+      <c r="L370" t="n">
         <v>1317</v>
       </c>
     </row>
@@ -19335,7 +17485,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F371" t="n">
@@ -19360,12 +17510,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L371" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M371" t="n">
+      <c r="L371" t="n">
         <v>2463</v>
       </c>
     </row>
@@ -19386,7 +17531,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F372" t="n">
@@ -19411,12 +17556,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L372" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M372" t="n">
+      <c r="L372" t="n">
         <v>3484</v>
       </c>
     </row>
@@ -19462,12 +17602,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L373" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M373" t="n">
+      <c r="L373" t="n">
         <v>798</v>
       </c>
     </row>
@@ -19513,12 +17648,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L374" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M374" t="n">
+      <c r="L374" t="n">
         <v>1548</v>
       </c>
     </row>
@@ -19564,12 +17694,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L375" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M375" t="n">
+      <c r="L375" t="n">
         <v>753</v>
       </c>
     </row>
@@ -19590,7 +17715,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -19615,12 +17740,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L376" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M376" t="n">
+      <c r="L376" t="n">
         <v>251</v>
       </c>
     </row>
@@ -19641,7 +17761,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F377" t="n">
@@ -19666,12 +17786,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L377" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M377" t="n">
+      <c r="L377" t="n">
         <v>389</v>
       </c>
     </row>
@@ -19717,12 +17832,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L378" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M378" t="n">
+      <c r="L378" t="n">
         <v>1280</v>
       </c>
     </row>
@@ -19768,12 +17878,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L379" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M379" t="n">
+      <c r="L379" t="n">
         <v>1161</v>
       </c>
     </row>
@@ -19819,12 +17924,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L380" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M380" t="n">
+      <c r="L380" t="n">
         <v>345</v>
       </c>
     </row>
@@ -19870,12 +17970,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L381" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M381" t="n">
+      <c r="L381" t="n">
         <v>3364</v>
       </c>
     </row>
@@ -19896,7 +17991,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F382" t="n">
@@ -19921,12 +18016,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L382" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M382" t="n">
+      <c r="L382" t="n">
         <v>1035</v>
       </c>
     </row>
@@ -19972,12 +18062,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L383" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M383" t="n">
+      <c r="L383" t="n">
         <v>3104</v>
       </c>
     </row>
@@ -19998,7 +18083,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F384" t="n">
@@ -20023,12 +18108,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L384" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M384" t="n">
+      <c r="L384" t="n">
         <v>1962</v>
       </c>
     </row>
@@ -20049,7 +18129,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F385" t="n">
@@ -20074,12 +18154,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L385" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M385" t="n">
+      <c r="L385" t="n">
         <v>319</v>
       </c>
     </row>
@@ -20100,7 +18175,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F386" t="n">
@@ -20125,12 +18200,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L386" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M386" t="n">
+      <c r="L386" t="n">
         <v>1682</v>
       </c>
     </row>
@@ -20151,7 +18221,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F387" t="n">
@@ -20176,12 +18246,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L387" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M387" t="n">
+      <c r="L387" t="n">
         <v>1317</v>
       </c>
     </row>
@@ -20202,7 +18267,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F388" t="n">
@@ -20227,12 +18292,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L388" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M388" t="n">
+      <c r="L388" t="n">
         <v>954</v>
       </c>
     </row>
@@ -20253,7 +18313,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F389" t="n">
@@ -20278,12 +18338,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L389" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M389" t="n">
+      <c r="L389" t="n">
         <v>282</v>
       </c>
     </row>
@@ -20329,12 +18384,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L390" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M390" t="n">
+      <c r="L390" t="n">
         <v>2394</v>
       </c>
     </row>
@@ -20355,7 +18405,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F391" t="n">
@@ -20380,12 +18430,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L391" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M391" t="n">
+      <c r="L391" t="n">
         <v>3460</v>
       </c>
     </row>
@@ -20431,12 +18476,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L392" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M392" t="n">
+      <c r="L392" t="n">
         <v>1552</v>
       </c>
     </row>
@@ -20457,7 +18497,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F393" t="n">
@@ -20482,12 +18522,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L393" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M393" t="n">
+      <c r="L393" t="n">
         <v>2460</v>
       </c>
     </row>
@@ -20508,7 +18543,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F394" t="n">
@@ -20533,12 +18568,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L394" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M394" t="n">
+      <c r="L394" t="n">
         <v>1502</v>
       </c>
     </row>
@@ -20559,7 +18589,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F395" t="n">
@@ -20584,12 +18614,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L395" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M395" t="n">
+      <c r="L395" t="n">
         <v>1556</v>
       </c>
     </row>
@@ -20610,7 +18635,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F396" t="n">
@@ -20635,12 +18660,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L396" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M396" t="n">
+      <c r="L396" t="n">
         <v>1035</v>
       </c>
     </row>
@@ -20661,7 +18681,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F397" t="n">
@@ -20686,12 +18706,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L397" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M397" t="n">
+      <c r="L397" t="n">
         <v>310</v>
       </c>
     </row>
@@ -20712,7 +18727,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F398" t="n">
@@ -20737,12 +18752,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L398" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M398" t="n">
+      <c r="L398" t="n">
         <v>1833</v>
       </c>
     </row>
@@ -20788,12 +18798,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L399" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M399" t="n">
+      <c r="L399" t="n">
         <v>1984</v>
       </c>
     </row>
@@ -20839,12 +18844,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L400" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M400" t="n">
+      <c r="L400" t="n">
         <v>465</v>
       </c>
     </row>
@@ -20890,12 +18890,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L401" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M401" t="n">
+      <c r="L401" t="n">
         <v>2943</v>
       </c>
     </row>
@@ -20916,7 +18911,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F402" t="n">
@@ -20941,12 +18936,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L402" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M402" t="n">
+      <c r="L402" t="n">
         <v>1228</v>
       </c>
     </row>
@@ -20967,7 +18957,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F403" t="n">
@@ -20992,12 +18982,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L403" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M403" t="n">
+      <c r="L403" t="n">
         <v>1210</v>
       </c>
     </row>
@@ -21043,12 +19028,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L404" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M404" t="n">
+      <c r="L404" t="n">
         <v>1230</v>
       </c>
     </row>
@@ -21094,12 +19074,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L405" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M405" t="n">
+      <c r="L405" t="n">
         <v>477</v>
       </c>
     </row>
@@ -21120,7 +19095,7 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F406" t="n">
@@ -21145,12 +19120,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L406" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M406" t="n">
+      <c r="L406" t="n">
         <v>3116</v>
       </c>
     </row>
@@ -21171,7 +19141,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F407" t="n">
@@ -21196,12 +19166,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L407" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M407" t="n">
+      <c r="L407" t="n">
         <v>928</v>
       </c>
     </row>
@@ -21247,12 +19212,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L408" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M408" t="n">
+      <c r="L408" t="n">
         <v>505</v>
       </c>
     </row>
@@ -21273,7 +19233,7 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -21298,12 +19258,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L409" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M409" t="n">
+      <c r="L409" t="n">
         <v>465</v>
       </c>
     </row>
@@ -21349,12 +19304,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L410" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M410" t="n">
+      <c r="L410" t="n">
         <v>168</v>
       </c>
     </row>
@@ -21375,7 +19325,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -21400,12 +19350,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L411" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M411" t="n">
+      <c r="L411" t="n">
         <v>1004</v>
       </c>
     </row>
@@ -21451,12 +19396,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L412" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M412" t="n">
+      <c r="L412" t="n">
         <v>1161</v>
       </c>
     </row>
@@ -21477,7 +19417,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -21502,12 +19442,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L413" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M413" t="n">
+      <c r="L413" t="n">
         <v>928</v>
       </c>
     </row>
@@ -21553,12 +19488,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L414" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M414" t="n">
+      <c r="L414" t="n">
         <v>204</v>
       </c>
     </row>
@@ -21579,7 +19509,7 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F415" t="n">
@@ -21604,12 +19534,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L415" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M415" t="n">
+      <c r="L415" t="n">
         <v>465</v>
       </c>
     </row>
@@ -21630,7 +19555,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F416" t="n">
@@ -21655,12 +19580,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L416" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M416" t="n">
+      <c r="L416" t="n">
         <v>1596</v>
       </c>
     </row>
@@ -21681,7 +19601,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F417" t="n">
@@ -21706,12 +19626,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L417" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M417" t="n">
+      <c r="L417" t="n">
         <v>1833</v>
       </c>
     </row>
@@ -21732,7 +19647,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F418" t="n">
@@ -21757,12 +19672,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L418" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M418" t="n">
+      <c r="L418" t="n">
         <v>602</v>
       </c>
     </row>
@@ -21808,12 +19718,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L419" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M419" t="n">
+      <c r="L419" t="n">
         <v>439</v>
       </c>
     </row>
@@ -21834,7 +19739,7 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F420" t="n">
@@ -21859,12 +19764,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L420" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M420" t="n">
+      <c r="L420" t="n">
         <v>1580</v>
       </c>
     </row>
@@ -21885,7 +19785,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F421" t="n">
@@ -21910,12 +19810,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L421" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M421" t="n">
+      <c r="L421" t="n">
         <v>505</v>
       </c>
     </row>
@@ -21936,7 +19831,7 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F422" t="n">
@@ -21961,12 +19856,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L422" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M422" t="n">
+      <c r="L422" t="n">
         <v>564</v>
       </c>
     </row>
@@ -21987,7 +19877,7 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -22012,12 +19902,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L423" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M423" t="n">
+      <c r="L423" t="n">
         <v>1538</v>
       </c>
     </row>
@@ -22038,7 +19923,7 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F424" t="n">
@@ -22063,12 +19948,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L424" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M424" t="n">
+      <c r="L424" t="n">
         <v>2763</v>
       </c>
     </row>
@@ -22089,7 +19969,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -22114,12 +19994,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L425" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M425" t="n">
+      <c r="L425" t="n">
         <v>605</v>
       </c>
     </row>
@@ -22140,7 +20015,7 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F426" t="n">
@@ -22165,12 +20040,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L426" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M426" t="n">
+      <c r="L426" t="n">
         <v>2460</v>
       </c>
     </row>
@@ -22191,7 +20061,7 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F427" t="n">
@@ -22216,12 +20086,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L427" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M427" t="n">
+      <c r="L427" t="n">
         <v>319</v>
       </c>
     </row>
@@ -22242,7 +20107,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -22267,12 +20132,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L428" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M428" t="n">
+      <c r="L428" t="n">
         <v>2420</v>
       </c>
     </row>
@@ -22318,12 +20178,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L429" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M429" t="n">
+      <c r="L429" t="n">
         <v>611</v>
       </c>
     </row>
@@ -22344,7 +20199,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F430" t="n">
@@ -22369,12 +20224,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L430" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M430" t="n">
+      <c r="L430" t="n">
         <v>3096</v>
       </c>
     </row>
@@ -22420,12 +20270,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L431" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M431" t="n">
+      <c r="L431" t="n">
         <v>1004</v>
       </c>
     </row>
@@ -22471,12 +20316,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L432" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M432" t="n">
+      <c r="L432" t="n">
         <v>690</v>
       </c>
     </row>
@@ -22522,12 +20362,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L433" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M433" t="n">
+      <c r="L433" t="n">
         <v>1020</v>
       </c>
     </row>
@@ -22548,7 +20383,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F434" t="n">
@@ -22573,12 +20408,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L434" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M434" t="n">
+      <c r="L434" t="n">
         <v>1116</v>
       </c>
     </row>
@@ -22624,12 +20454,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L435" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M435" t="n">
+      <c r="L435" t="n">
         <v>3712</v>
       </c>
     </row>
@@ -22675,12 +20500,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L436" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M436" t="n">
+      <c r="L436" t="n">
         <v>960</v>
       </c>
     </row>
@@ -22701,7 +20521,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F437" t="n">
@@ -22726,12 +20546,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L437" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M437" t="n">
+      <c r="L437" t="n">
         <v>2736</v>
       </c>
     </row>
@@ -22752,7 +20567,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F438" t="n">
@@ -22777,12 +20592,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L438" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M438" t="n">
+      <c r="L438" t="n">
         <v>1431</v>
       </c>
     </row>
@@ -22803,7 +20613,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F439" t="n">
@@ -22828,12 +20638,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L439" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M439" t="n">
+      <c r="L439" t="n">
         <v>1380</v>
       </c>
     </row>
@@ -22854,7 +20659,7 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F440" t="n">
@@ -22879,12 +20684,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L440" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M440" t="n">
+      <c r="L440" t="n">
         <v>902</v>
       </c>
     </row>
@@ -22905,7 +20705,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F441" t="n">
@@ -22930,12 +20730,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L441" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M441" t="n">
+      <c r="L441" t="n">
         <v>1650</v>
       </c>
     </row>
@@ -22981,12 +20776,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L442" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M442" t="n">
+      <c r="L442" t="n">
         <v>1020</v>
       </c>
     </row>
@@ -23032,12 +20822,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L443" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M443" t="n">
+      <c r="L443" t="n">
         <v>2328</v>
       </c>
     </row>
@@ -23083,12 +20868,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L444" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M444" t="n">
+      <c r="L444" t="n">
         <v>2784</v>
       </c>
     </row>
@@ -23109,7 +20889,7 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F445" t="n">
@@ -23134,12 +20914,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L445" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M445" t="n">
+      <c r="L445" t="n">
         <v>874</v>
       </c>
     </row>
@@ -23160,7 +20935,7 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F446" t="n">
@@ -23185,12 +20960,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L446" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M446" t="n">
+      <c r="L446" t="n">
         <v>390</v>
       </c>
     </row>
@@ -23211,7 +20981,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F447" t="n">
@@ -23236,12 +21006,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L447" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M447" t="n">
+      <c r="L447" t="n">
         <v>451</v>
       </c>
     </row>
@@ -23262,7 +21027,7 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F448" t="n">
@@ -23287,12 +21052,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L448" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M448" t="n">
+      <c r="L448" t="n">
         <v>1642</v>
       </c>
     </row>
@@ -23313,7 +21073,7 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F449" t="n">
@@ -23338,12 +21098,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L449" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M449" t="n">
+      <c r="L449" t="n">
         <v>1512</v>
       </c>
     </row>
@@ -23364,7 +21119,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F450" t="n">
@@ -23389,12 +21144,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L450" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M450" t="n">
+      <c r="L450" t="n">
         <v>1548</v>
       </c>
     </row>
@@ -23415,7 +21165,7 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F451" t="n">
@@ -23440,12 +21190,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L451" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M451" t="n">
+      <c r="L451" t="n">
         <v>477</v>
       </c>
     </row>
@@ -23466,7 +21211,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F452" t="n">
@@ -23491,12 +21236,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L452" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M452" t="n">
+      <c r="L452" t="n">
         <v>1856</v>
       </c>
     </row>
@@ -23517,7 +21257,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F453" t="n">
@@ -23542,12 +21282,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L453" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M453" t="n">
+      <c r="L453" t="n">
         <v>638</v>
       </c>
     </row>
@@ -23568,7 +21303,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F454" t="n">
@@ -23593,12 +21328,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L454" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M454" t="n">
+      <c r="L454" t="n">
         <v>638</v>
       </c>
     </row>
@@ -23619,7 +21349,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F455" t="n">
@@ -23644,12 +21374,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L455" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M455" t="n">
+      <c r="L455" t="n">
         <v>874</v>
       </c>
     </row>
@@ -23670,7 +21395,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -23695,12 +21420,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L456" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M456" t="n">
+      <c r="L456" t="n">
         <v>614</v>
       </c>
     </row>
@@ -23746,12 +21466,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L457" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M457" t="n">
+      <c r="L457" t="n">
         <v>2232</v>
       </c>
     </row>
@@ -23797,12 +21512,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L458" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M458" t="n">
+      <c r="L458" t="n">
         <v>602</v>
       </c>
     </row>
@@ -23823,7 +21533,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F459" t="n">
@@ -23848,12 +21558,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L459" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M459" t="n">
+      <c r="L459" t="n">
         <v>1856</v>
       </c>
     </row>
@@ -23874,7 +21579,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F460" t="n">
@@ -23899,12 +21604,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L460" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M460" t="n">
+      <c r="L460" t="n">
         <v>1035</v>
       </c>
     </row>
@@ -23950,12 +21650,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L461" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M461" t="n">
+      <c r="L461" t="n">
         <v>1652</v>
       </c>
     </row>
@@ -23976,7 +21671,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F462" t="n">
@@ -24001,12 +21696,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L462" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M462" t="n">
+      <c r="L462" t="n">
         <v>2337</v>
       </c>
     </row>
@@ -24052,12 +21742,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L463" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M463" t="n">
+      <c r="L463" t="n">
         <v>3884</v>
       </c>
     </row>
@@ -24078,7 +21763,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F464" t="n">
@@ -24103,12 +21788,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L464" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M464" t="n">
+      <c r="L464" t="n">
         <v>912</v>
       </c>
     </row>
@@ -24154,12 +21834,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L465" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M465" t="n">
+      <c r="L465" t="n">
         <v>84</v>
       </c>
     </row>
@@ -24180,7 +21855,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F466" t="n">
@@ -24205,12 +21880,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L466" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M466" t="n">
+      <c r="L466" t="n">
         <v>3304</v>
       </c>
     </row>
@@ -24231,7 +21901,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F467" t="n">
@@ -24256,12 +21926,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="L467" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M467" t="n">
+      <c r="L467" t="n">
         <v>912</v>
       </c>
     </row>
@@ -24307,12 +21972,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L468" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M468" t="n">
+      <c r="L468" t="n">
         <v>3116</v>
       </c>
     </row>
@@ -24333,7 +21993,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F469" t="n">
@@ -24358,12 +22018,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L469" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M469" t="n">
+      <c r="L469" t="n">
         <v>408</v>
       </c>
     </row>
@@ -24384,7 +22039,7 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F470" t="n">
@@ -24409,12 +22064,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L470" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M470" t="n">
+      <c r="L470" t="n">
         <v>3712</v>
       </c>
     </row>
@@ -24460,12 +22110,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L471" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M471" t="n">
+      <c r="L471" t="n">
         <v>84</v>
       </c>
     </row>
@@ -24511,12 +22156,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L472" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M472" t="n">
+      <c r="L472" t="n">
         <v>306</v>
       </c>
     </row>
@@ -24537,7 +22177,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F473" t="n">
@@ -24562,12 +22202,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L473" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M473" t="n">
+      <c r="L473" t="n">
         <v>3364</v>
       </c>
     </row>
@@ -24588,7 +22223,7 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F474" t="n">
@@ -24613,12 +22248,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L474" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M474" t="n">
+      <c r="L474" t="n">
         <v>1558</v>
       </c>
     </row>
@@ -24639,7 +22269,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F475" t="n">
@@ -24664,12 +22294,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L475" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M475" t="n">
+      <c r="L475" t="n">
         <v>776</v>
       </c>
     </row>
@@ -24715,12 +22340,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L476" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M476" t="n">
+      <c r="L476" t="n">
         <v>3284</v>
       </c>
     </row>
@@ -24766,12 +22386,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L477" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M477" t="n">
+      <c r="L477" t="n">
         <v>2104</v>
       </c>
     </row>
@@ -24817,12 +22432,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L478" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M478" t="n">
+      <c r="L478" t="n">
         <v>1222</v>
       </c>
     </row>
@@ -24868,12 +22478,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L479" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M479" t="n">
+      <c r="L479" t="n">
         <v>1248</v>
       </c>
     </row>
@@ -24894,7 +22499,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F480" t="n">
@@ -24919,12 +22524,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L480" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M480" t="n">
+      <c r="L480" t="n">
         <v>252</v>
       </c>
     </row>
@@ -24945,7 +22545,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F481" t="n">
@@ -24970,12 +22570,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L481" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M481" t="n">
+      <c r="L481" t="n">
         <v>1167</v>
       </c>
     </row>
@@ -25021,12 +22616,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L482" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M482" t="n">
+      <c r="L482" t="n">
         <v>2104</v>
       </c>
     </row>
@@ -25047,7 +22637,7 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F483" t="n">
@@ -25072,12 +22662,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L483" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M483" t="n">
+      <c r="L483" t="n">
         <v>3364</v>
       </c>
     </row>
@@ -25098,7 +22683,7 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F484" t="n">
@@ -25123,12 +22708,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L484" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M484" t="n">
+      <c r="L484" t="n">
         <v>2456</v>
       </c>
     </row>
@@ -25174,12 +22754,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L485" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M485" t="n">
+      <c r="L485" t="n">
         <v>416</v>
       </c>
     </row>
@@ -25200,7 +22775,7 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F486" t="n">
@@ -25225,12 +22800,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L486" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M486" t="n">
+      <c r="L486" t="n">
         <v>1682</v>
       </c>
     </row>
@@ -25251,7 +22821,7 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F487" t="n">
@@ -25276,12 +22846,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L487" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M487" t="n">
+      <c r="L487" t="n">
         <v>3104</v>
       </c>
     </row>
@@ -25302,7 +22867,7 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F488" t="n">
@@ -25327,12 +22892,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L488" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M488" t="n">
+      <c r="L488" t="n">
         <v>1652</v>
       </c>
     </row>
@@ -25378,12 +22938,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L489" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M489" t="n">
+      <c r="L489" t="n">
         <v>1682</v>
       </c>
     </row>
@@ -25429,12 +22984,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L490" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M490" t="n">
+      <c r="L490" t="n">
         <v>1833</v>
       </c>
     </row>
@@ -25480,12 +23030,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L491" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M491" t="n">
+      <c r="L491" t="n">
         <v>774</v>
       </c>
     </row>
@@ -25531,12 +23076,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L492" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M492" t="n">
+      <c r="L492" t="n">
         <v>3484</v>
       </c>
     </row>
@@ -25557,7 +23097,7 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F493" t="n">
@@ -25582,12 +23122,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L493" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M493" t="n">
+      <c r="L493" t="n">
         <v>1842</v>
       </c>
     </row>
@@ -25633,12 +23168,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L494" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M494" t="n">
+      <c r="L494" t="n">
         <v>390</v>
       </c>
     </row>
@@ -25659,7 +23189,7 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F495" t="n">
@@ -25684,12 +23214,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L495" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M495" t="n">
+      <c r="L495" t="n">
         <v>3116</v>
       </c>
     </row>
@@ -25710,7 +23235,7 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F496" t="n">
@@ -25735,12 +23260,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="L496" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M496" t="n">
+      <c r="L496" t="n">
         <v>1548</v>
       </c>
     </row>
@@ -25761,7 +23281,7 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F497" t="n">
@@ -25786,12 +23306,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="L497" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="M497" t="n">
+      <c r="L497" t="n">
         <v>753</v>
       </c>
     </row>
@@ -25812,7 +23327,7 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F498" t="n">
@@ -25837,12 +23352,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="L498" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M498" t="n">
+      <c r="L498" t="n">
         <v>1052</v>
       </c>
     </row>
@@ -25863,7 +23373,7 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -25888,12 +23398,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L499" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M499" t="n">
+      <c r="L499" t="n">
         <v>981</v>
       </c>
     </row>
@@ -25914,7 +23419,7 @@
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -25939,12 +23444,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="L500" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="M500" t="n">
+      <c r="L500" t="n">
         <v>1742</v>
       </c>
     </row>
@@ -25965,7 +23465,7 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="F501" t="n">
@@ -25990,12 +23490,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="L501" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="M501" t="n">
+      <c r="L501" t="n">
         <v>451</v>
       </c>
     </row>
